--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_46.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3977208.182811019</v>
+        <v>3978286.44484618</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13582731.7327678</v>
+        <v>13593507.14668309</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13582731.7327678</v>
+        <v>13593507.14668309</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>561.0660572105371</v>
+        <v>6591.459428645569</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561.0660572105371</v>
+        <v>6591.459428645569</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21567155.6502195</v>
+        <v>21564969.75020239</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.347322035758213</v>
+        <v>3.343301935256587</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>5.722467174369981</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964851</v>
+        <v>85.41253966161939</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T3" t="n">
-        <v>374</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U3" t="n">
         <v>374</v>
@@ -796,13 +796,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>176.5671455182964</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>82.70388171325763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,73 +970,73 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>330.0284079411381</v>
+      </c>
+      <c r="I6" t="n">
+        <v>209.4985557026693</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>144.7989632036872</v>
+      </c>
+      <c r="R6" t="n">
+        <v>273.5500579169974</v>
+      </c>
+      <c r="S6" t="n">
+        <v>62.44885845517734</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.464774651476091</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1957842884886531</v>
+      </c>
+      <c r="V6" t="n">
         <v>374</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>342.6720972219126</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>209.5726123064429</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>145.073529241423</v>
-      </c>
-      <c r="R6" t="n">
-        <v>133.6519859716245</v>
-      </c>
-      <c r="S6" t="n">
-        <v>62.48881128536601</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.473444462796863</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1959257979225981</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>129.2251536760129</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>139.0130832731133</v>
+        <v>374</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>151.8437451380612</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>374</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>142.0601778525742</v>
@@ -1428,7 +1428,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>317.3734759809475</v>
+        <v>314.4174191251558</v>
       </c>
       <c r="X11" t="n">
         <v>271.2818334606677</v>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
         <v>3.993158516536766</v>
@@ -1495,7 +1495,7 @@
         <v>179.932929367851</v>
       </c>
       <c r="S12" t="n">
-        <v>131.7003678891396</v>
+        <v>314.8596346682833</v>
       </c>
       <c r="T12" t="n">
         <v>81.34934068921194</v>
@@ -1510,7 +1510,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>282.0220062245311</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1611,16 +1611,16 @@
         <v>89.33915573984979</v>
       </c>
       <c r="E14" t="n">
-        <v>83.36328960686865</v>
+        <v>80.40723275107717</v>
       </c>
       <c r="F14" t="n">
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H14" t="n">
-        <v>72.7233722713666</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U14" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1668,7 +1668,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>272.206576604876</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>190.3174326828064</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
@@ -1696,13 +1696,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H15" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>183.1592667791436</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>363.0921961469944</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S15" t="n">
         <v>131.7003678891396</v>
       </c>
       <c r="T15" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M16" t="n">
         <v>101.5443818943532</v>
@@ -1799,19 +1799,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O16" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P16" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R16" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S16" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H17" t="n">
-        <v>72.7233722713666</v>
+        <v>69.76731541558893</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.9849209967825</v>
+        <v>142.0601778525742</v>
       </c>
       <c r="T17" t="n">
         <v>259.5690792160011</v>
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>168.9109734293304</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.993158516536766</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>179.932929367851</v>
@@ -1975,13 +1975,13 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16125598660182</v>
+        <v>262.3205227657453</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.0601778525742</v>
@@ -2139,7 +2139,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>317.3734759809475</v>
+        <v>314.4174191251558</v>
       </c>
       <c r="X20" t="n">
         <v>271.2818334606677</v>
@@ -2158,7 +2158,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>223.2591792246629</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -2176,7 +2176,7 @@
         <v>3.959653224156966</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>183.1592667791436</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.36239741264436</v>
+        <v>78.40634055685268</v>
       </c>
       <c r="H23" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.0601778525742</v>
@@ -2370,7 +2370,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U23" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V23" t="n">
         <v>308.8510241668239</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>223.2591792246631</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H24" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2446,22 +2446,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T24" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>261.5506595452778</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M25" t="n">
         <v>101.5443818943532</v>
@@ -2510,19 +2510,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O25" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P25" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q25" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R25" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S25" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H26" t="n">
-        <v>72.7233722713666</v>
+        <v>73.64811541557516</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,28 +2629,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>210.0969536768462</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H27" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2683,19 +2683,19 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16125598660182</v>
+        <v>391.891778383831</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>81.36239741264436</v>
       </c>
       <c r="H29" t="n">
-        <v>73.64811541557516</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S29" t="n">
         <v>142.0601778525742</v>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>246.7158234254702</v>
+        <v>246.7158234254703</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.993158516536777</v>
@@ -2920,7 +2920,7 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T30" t="n">
-        <v>81.34934068921193</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U30" t="n">
         <v>79.16125598660184</v>
@@ -3042,10 +3042,10 @@
         <v>81.36239741264436</v>
       </c>
       <c r="H32" t="n">
-        <v>73.64811541557516</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.9247431442085484</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.993158516536777</v>
@@ -3154,25 +3154,25 @@
         <v>179.932929367851</v>
       </c>
       <c r="S33" t="n">
-        <v>131.7003678891396</v>
+        <v>452.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921193</v>
+        <v>264.5086074683554</v>
       </c>
       <c r="U33" t="n">
         <v>79.16125598660184</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>261.5506595452779</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3276,7 +3276,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>56.65754055685251</v>
+        <v>52.77674055694824</v>
       </c>
       <c r="H35" t="n">
         <v>48.72337227136661</v>
@@ -3349,19 +3349,19 @@
         <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>83.94446820508263</v>
       </c>
       <c r="H36" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>20.65591485933</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>155.932929367851</v>
@@ -3400,16 +3400,16 @@
         <v>55.16125598660184</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3513,10 +3513,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.36239741264433</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
-        <v>48.7233722713666</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U38" t="n">
-        <v>304.109698558661</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V38" t="n">
         <v>284.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>293.3734759809475</v>
+        <v>288.7878191252514</v>
       </c>
       <c r="X38" t="n">
         <v>247.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>165.6125758270146</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3580,22 +3580,22 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>92.3527202103913</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>86.11207851983707</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,19 +3631,19 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T39" t="n">
-        <v>57.34934068921194</v>
+        <v>57.34934068921193</v>
       </c>
       <c r="U39" t="n">
-        <v>55.16125598660182</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V39" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
         <v>54.39139276613435</v>
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>77.54438189435319</v>
+        <v>77.54438189435318</v>
       </c>
       <c r="N40" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O40" t="n">
-        <v>207.000383751146</v>
+        <v>207.0003837511461</v>
       </c>
       <c r="P40" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q40" t="n">
-        <v>328.4422664255979</v>
+        <v>328.442266425598</v>
       </c>
       <c r="R40" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S40" t="n">
-        <v>6.468578063511188</v>
+        <v>6.468578063511176</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>117.3553209967828</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T41" t="n">
         <v>235.5690792160011</v>
@@ -3798,7 +3798,7 @@
         <v>284.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>293.3734759809475</v>
+        <v>288.7878191252514</v>
       </c>
       <c r="X41" t="n">
         <v>247.2818334606677</v>
@@ -3814,19 +3814,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>16.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>81.35810497732919</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>57.34934068921193</v>
+        <v>141.2938088942944</v>
       </c>
       <c r="U42" t="n">
-        <v>55.16125598660184</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V42" t="n">
         <v>69.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3987,10 +3987,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264435</v>
+        <v>52.77674055694106</v>
       </c>
       <c r="H44" t="n">
-        <v>48.01851541557478</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U44" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V44" t="n">
         <v>284.8510241668239</v>
@@ -4054,22 +4054,22 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>2.937686897702633</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>76.2528077648651</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>100.7551623411772</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>155.932929367851</v>
+        <v>500.932929367851</v>
       </c>
       <c r="S45" t="n">
-        <v>107.7003678891396</v>
+        <v>452.7003678891396</v>
       </c>
       <c r="T45" t="n">
-        <v>57.34934068921193</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U45" t="n">
-        <v>55.16125598660184</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V45" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>87.37314290982852</v>
@@ -4120,7 +4120,7 @@
         <v>74.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4163,25 +4163,25 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N46" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O46" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P46" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q46" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R46" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S46" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.9141473750823</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C2" t="n">
-        <v>56.93982591751266</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426109873</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183748</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F2" t="n">
-        <v>37.1498521248558</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>35.70026987310099</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4324,22 +4324,22 @@
         <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>691.4180850251257</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M2" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
+        <v>1067.075793611129</v>
+      </c>
+      <c r="P2" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606416</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178446</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698501</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861896</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165456</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138509</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190969</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>837.0935333277771</v>
       </c>
       <c r="T3" t="n">
-        <v>773.5612863652389</v>
+        <v>832.5836599424478</v>
       </c>
       <c r="U3" t="n">
-        <v>395.783508587461</v>
+        <v>454.8058821646699</v>
       </c>
       <c r="V3" t="n">
-        <v>381.1262690000669</v>
+        <v>440.1486425772758</v>
       </c>
       <c r="W3" t="n">
-        <v>348.4261246467048</v>
+        <v>261.7979905385926</v>
       </c>
       <c r="X3" t="n">
-        <v>328.3627514695457</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="Y3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.7346173614335</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="C4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="D4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="E4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="F4" t="n">
-        <v>801.0157630520778</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="G4" t="n">
-        <v>954.6044240209303</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="H4" t="n">
-        <v>1125.74</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="I4" t="n">
-        <v>1125.74</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J4" t="n">
-        <v>1496</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>139.176451535273</v>
+        <v>70.37478771712394</v>
       </c>
       <c r="T4" t="n">
-        <v>139.176451535273</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>326.8026065500028</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V4" t="n">
-        <v>525.6239994359488</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="W4" t="n">
-        <v>525.6239994359488</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="X4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="Y4" t="n">
-        <v>676.6547904601423</v>
+        <v>652.7906108062779</v>
       </c>
     </row>
     <row r="5">
@@ -4534,46 +4534,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>770.4399999999999</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
         <v>1125.74</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>587.7429389175309</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="C6" t="n">
-        <v>587.7429389175309</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="D6" t="n">
-        <v>587.7429389175309</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1073.225316559763</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1010.145661554534</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1005.635788169204</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1005.43802626164</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>627.6602484838622</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>594.9601041305001</v>
       </c>
       <c r="X6" t="n">
-        <v>965.5207166953087</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="Y6" t="n">
-        <v>965.5207166953087</v>
+        <v>574.8967309533409</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>987.0779490488756</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>987.0779490488756</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>987.0779490488756</v>
+        <v>85.85883935008918</v>
       </c>
       <c r="E7" t="n">
-        <v>987.0779490488756</v>
+        <v>203.6877435615022</v>
       </c>
       <c r="F7" t="n">
-        <v>987.0779490488756</v>
+        <v>328.0487161534377</v>
       </c>
       <c r="G7" t="n">
-        <v>987.0779490488756</v>
+        <v>481.6391623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>987.0779490488756</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="I7" t="n">
-        <v>987.0779490488756</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J7" t="n">
-        <v>1357.337949048876</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
@@ -4746,22 +4746,22 @@
         <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>465.3348468790587</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>664.1562397650047</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>836.0471580246821</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>987.0779490488756</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>987.0779490488756</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>770.4399999999999</v>
+        <v>1140.7</v>
       </c>
       <c r="M8" t="n">
-        <v>770.4399999999999</v>
+        <v>1140.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1199.364206388871</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1070.572551977265</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="C9" t="n">
-        <v>1070.572551977265</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="D9" t="n">
-        <v>719.1203429896864</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E9" t="n">
         <v>372.9869114524009</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1205.829856111428</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S9" t="n">
-        <v>1142.709844712069</v>
+        <v>818.3832082556585</v>
       </c>
       <c r="T9" t="n">
-        <v>1138.191213941567</v>
+        <v>440.6054304778806</v>
       </c>
       <c r="U9" t="n">
-        <v>1137.99330909518</v>
+        <v>440.4076685703163</v>
       </c>
       <c r="V9" t="n">
-        <v>1123.336069507786</v>
+        <v>425.7504289829222</v>
       </c>
       <c r="W9" t="n">
-        <v>1090.635925154424</v>
+        <v>393.0502846295601</v>
       </c>
       <c r="X9" t="n">
-        <v>1070.572551977265</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="Y9" t="n">
-        <v>1070.572551977265</v>
+        <v>372.9869114524009</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>264.3336096174874</v>
+        <v>293.5414260624483</v>
       </c>
       <c r="C10" t="n">
-        <v>390.3356154359232</v>
+        <v>419.5434318808841</v>
       </c>
       <c r="D10" t="n">
-        <v>390.3356154359232</v>
+        <v>532.8625760058842</v>
       </c>
       <c r="E10" t="n">
-        <v>508.1645196473362</v>
+        <v>650.6914802172972</v>
       </c>
       <c r="F10" t="n">
-        <v>632.5254922392717</v>
+        <v>725.8628264784263</v>
       </c>
       <c r="G10" t="n">
-        <v>786.1141532081242</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="H10" t="n">
-        <v>786.1141532081242</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="I10" t="n">
-        <v>1012.723127881912</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J10" t="n">
-        <v>1382.983127881912</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="W10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="X10" t="n">
-        <v>41.16697127216297</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="Y10" t="n">
-        <v>152.5762719511952</v>
+        <v>181.7840883961562</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C11" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D11" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F11" t="n">
-        <v>207.562191600011</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G11" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J11" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K11" t="n">
-        <v>1202.951894293937</v>
+        <v>1201.881894293937</v>
       </c>
       <c r="L11" t="n">
-        <v>1845.461894293937</v>
+        <v>1843.401894293937</v>
       </c>
       <c r="M11" t="n">
-        <v>2234.549243836214</v>
+        <v>1843.401894293937</v>
       </c>
       <c r="N11" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O11" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R11" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X11" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.110657215864</v>
+        <v>816.7882329734396</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.605695149683</v>
+        <v>452.0408466648342</v>
       </c>
       <c r="D12" t="n">
-        <v>749.1534861621044</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0200546248188</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F12" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G12" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S12" t="n">
-        <v>1938.448397028141</v>
+        <v>1753.359036645168</v>
       </c>
       <c r="T12" t="n">
-        <v>1856.277345826917</v>
+        <v>1671.187985443944</v>
       </c>
       <c r="U12" t="n">
-        <v>1776.316481193986</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V12" t="n">
-        <v>1681.861261808612</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W12" t="n">
-        <v>1569.36313765727</v>
+        <v>1384.273777274297</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.492424299158</v>
+        <v>1284.412424299158</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.309199282861</v>
+        <v>1205.22919928286</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C13" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D13" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E13" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F13" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G13" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H13" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I13" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J13" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M13" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N13" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R13" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T13" t="n">
-        <v>159.3041526995475</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U13" t="n">
-        <v>327.6791351738997</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V13" t="n">
-        <v>448.2905280598457</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W13" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X13" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y13" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.5184060421567</v>
+        <v>593.4524900262059</v>
       </c>
       <c r="C14" t="n">
-        <v>466.7461047866073</v>
+        <v>463.6801887706564</v>
       </c>
       <c r="D14" t="n">
-        <v>376.5045333322136</v>
+        <v>373.4386173162627</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F14" t="n">
-        <v>207.562191600011</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G14" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K14" t="n">
-        <v>736.1134691180577</v>
+        <v>1001.294971748371</v>
       </c>
       <c r="L14" t="n">
-        <v>1004.304971748371</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="M14" t="n">
-        <v>1646.814971748371</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N14" t="n">
-        <v>1646.814971748371</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O14" t="n">
-        <v>1809.956778005698</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P14" t="n">
-        <v>2008.265727912157</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T14" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.889943810873</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X14" t="n">
-        <v>951.383805676885</v>
+        <v>948.317889660934</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.1439746841512</v>
+        <v>756.0780586682004</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>492.6258087310154</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C15" t="n">
-        <v>452.1208466648343</v>
+        <v>961.2926312902318</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9110619196801</v>
+        <v>609.8404223026535</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0200546248188</v>
+        <v>587.9494150077923</v>
       </c>
       <c r="F15" t="n">
-        <v>59.95314317241791</v>
+        <v>244.8825035553913</v>
       </c>
       <c r="G15" t="n">
-        <v>55.91964972137067</v>
+        <v>240.8490101043441</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>236.8493603829734</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1886.469711280663</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S15" t="n">
-        <v>1753.439036645168</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T15" t="n">
-        <v>1671.267985443944</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1591.307120811013</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V15" t="n">
-        <v>1496.851901425639</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W15" t="n">
-        <v>1384.353777274297</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X15" t="n">
-        <v>1284.492424299158</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y15" t="n">
-        <v>881.0667750404363</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C16" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D16" t="n">
-        <v>769.5684225835375</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E16" t="n">
-        <v>809.1873267949505</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F16" t="n">
-        <v>855.338299386886</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G16" t="n">
-        <v>931.1543456016401</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H16" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I16" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J16" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M16" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N16" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R16" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8075321249603</v>
+        <v>327.5991351738998</v>
       </c>
       <c r="V16" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2105280598458</v>
       </c>
       <c r="W16" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X16" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y16" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.5184060421567</v>
+        <v>593.4524900262197</v>
       </c>
       <c r="C17" t="n">
-        <v>466.7461047866073</v>
+        <v>463.6801887706703</v>
       </c>
       <c r="D17" t="n">
-        <v>376.5045333322136</v>
+        <v>373.4386173162765</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2991902949725</v>
+        <v>289.2332742790355</v>
       </c>
       <c r="F17" t="n">
-        <v>207.562191600011</v>
+        <v>204.496275584074</v>
       </c>
       <c r="G17" t="n">
-        <v>125.3779517892592</v>
+        <v>122.3120357733222</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K17" t="n">
-        <v>736.1134691180577</v>
+        <v>1001.294971748371</v>
       </c>
       <c r="L17" t="n">
-        <v>954.0495916306205</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="M17" t="n">
-        <v>1596.559591630621</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N17" t="n">
-        <v>2234.549243836214</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O17" t="n">
-        <v>2397.691050093541</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2592.000000000014</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870856</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748928</v>
       </c>
       <c r="U17" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810887</v>
       </c>
       <c r="V17" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329246</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.405859677559</v>
+        <v>1222.339943661622</v>
       </c>
       <c r="X17" t="n">
-        <v>951.383805676885</v>
+        <v>948.3178896609479</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.1439746841512</v>
+        <v>756.0780586682142</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141.110657215864</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C18" t="n">
-        <v>776.3632709072585</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D18" t="n">
-        <v>749.1534861621044</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0200546248188</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F18" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G18" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1697.725723622128</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V18" t="n">
-        <v>1603.270504236754</v>
+        <v>1172.529477183215</v>
       </c>
       <c r="W18" t="n">
-        <v>1490.772380085412</v>
+        <v>735.7889287894483</v>
       </c>
       <c r="X18" t="n">
-        <v>1390.911027110273</v>
+        <v>635.9275758143093</v>
       </c>
       <c r="Y18" t="n">
-        <v>1311.727802093975</v>
+        <v>556.744350798012</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5684225835375</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E19" t="n">
-        <v>809.1873267949505</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F19" t="n">
-        <v>855.338299386886</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G19" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H19" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I19" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J19" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R19" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T19" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8075321249603</v>
+        <v>327.5991351738998</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2105280598458</v>
       </c>
       <c r="W19" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C20" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D20" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F20" t="n">
-        <v>207.562191600011</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G20" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>560.4418942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K20" t="n">
-        <v>984.677799142267</v>
+        <v>775.8802050736419</v>
       </c>
       <c r="L20" t="n">
-        <v>1202.61392165483</v>
+        <v>1417.400205073642</v>
       </c>
       <c r="M20" t="n">
-        <v>1202.61392165483</v>
+        <v>1589.029243836214</v>
       </c>
       <c r="N20" t="n">
-        <v>1202.61392165483</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O20" t="n">
-        <v>1365.755727912157</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P20" t="n">
-        <v>2008.265727912157</v>
+        <v>2592</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X20" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1326.120017598837</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.605695149683</v>
+        <v>1285.535055532656</v>
       </c>
       <c r="D21" t="n">
-        <v>749.1534861621044</v>
+        <v>934.0828465450777</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0200546248188</v>
+        <v>587.9494150077921</v>
       </c>
       <c r="F21" t="n">
-        <v>59.95314317241791</v>
+        <v>244.8825035553912</v>
       </c>
       <c r="G21" t="n">
-        <v>55.91964972137067</v>
+        <v>240.849010104344</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>236.8493603829733</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V21" t="n">
-        <v>1681.861261808612</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W21" t="n">
-        <v>1569.36313765727</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X21" t="n">
-        <v>1469.501784682131</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y21" t="n">
-        <v>1390.318559665834</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5684225835375</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E22" t="n">
-        <v>809.1873267949505</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F22" t="n">
-        <v>855.338299386886</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J22" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R22" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W22" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.5184060421568</v>
+        <v>593.4524900262056</v>
       </c>
       <c r="C23" t="n">
-        <v>466.7461047866074</v>
+        <v>463.6801887706562</v>
       </c>
       <c r="D23" t="n">
-        <v>376.5045333322136</v>
+        <v>373.4386173162624</v>
       </c>
       <c r="E23" t="n">
-        <v>292.2991902949726</v>
+        <v>289.2332742790214</v>
       </c>
       <c r="F23" t="n">
-        <v>207.5621916000111</v>
+        <v>204.4962755840599</v>
       </c>
       <c r="G23" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>134.440205073642</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K23" t="n">
-        <v>310.1117798977626</v>
+        <v>775.8802050736419</v>
       </c>
       <c r="L23" t="n">
-        <v>528.0479024103255</v>
+        <v>1417.400205073642</v>
       </c>
       <c r="M23" t="n">
-        <v>1004.304971748371</v>
+        <v>1589.029243836211</v>
       </c>
       <c r="N23" t="n">
-        <v>1646.814971748371</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O23" t="n">
-        <v>1809.956778005698</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P23" t="n">
-        <v>2008.265727912157</v>
+        <v>2592</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U23" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V23" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.405859677559</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X23" t="n">
-        <v>951.383805676885</v>
+        <v>948.3178896609338</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.1439746841513</v>
+        <v>756.0780586682001</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.6258087310154</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C24" t="n">
-        <v>452.1208466648343</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9110619196801</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F24" t="n">
-        <v>59.95314317241794</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G24" t="n">
-        <v>55.91964972137069</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S24" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T24" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V24" t="n">
-        <v>1357.618837566188</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W24" t="n">
-        <v>920.8782891724215</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X24" t="n">
-        <v>821.0169361972826</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y24" t="n">
-        <v>556.824350798012</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.6672726401017</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4592784585375</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5684225835375</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E25" t="n">
-        <v>809.1873267949505</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F25" t="n">
-        <v>855.338299386886</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1543456016401</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.968674039726</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J25" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R25" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X25" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.4524900262056</v>
+        <v>597.4524900262059</v>
       </c>
       <c r="C26" t="n">
-        <v>467.6801887706562</v>
+        <v>467.6801887706564</v>
       </c>
       <c r="D26" t="n">
-        <v>377.4386173162624</v>
+        <v>377.4386173162627</v>
       </c>
       <c r="E26" t="n">
-        <v>293.2332742790214</v>
+        <v>293.2332742790216</v>
       </c>
       <c r="F26" t="n">
-        <v>208.4962755840599</v>
+        <v>208.4962755840601</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3120357733081</v>
+        <v>126.3120357733083</v>
       </c>
       <c r="H26" t="n">
-        <v>52.85408398404886</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6226,7 +6226,7 @@
         <v>1419.460205073642</v>
       </c>
       <c r="M26" t="n">
-        <v>2061.970205073644</v>
+        <v>1592.039243836214</v>
       </c>
       <c r="N26" t="n">
         <v>2234.549243836214</v>
@@ -6250,7 +6250,7 @@
         <v>2190.313881748914</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.889943810872</v>
+        <v>1858.889943810873</v>
       </c>
       <c r="V26" t="n">
         <v>1546.919212329232</v>
@@ -6259,10 +6259,10 @@
         <v>1226.339943661608</v>
       </c>
       <c r="X26" t="n">
-        <v>952.3178896609338</v>
+        <v>952.317889660934</v>
       </c>
       <c r="Y26" t="n">
-        <v>760.0780586682001</v>
+        <v>760.0780586682004</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>353.3927448715644</v>
+        <v>1010.230601035979</v>
       </c>
       <c r="C27" t="n">
-        <v>312.8877828053833</v>
+        <v>969.7256389697984</v>
       </c>
       <c r="D27" t="n">
-        <v>100.6686376772558</v>
+        <v>618.27342998222</v>
       </c>
       <c r="E27" t="n">
-        <v>78.77763038239453</v>
+        <v>596.3824226873588</v>
       </c>
       <c r="F27" t="n">
-        <v>59.95314317241791</v>
+        <v>253.3155112349579</v>
       </c>
       <c r="G27" t="n">
-        <v>55.91964972137067</v>
+        <v>249.2820177839106</v>
       </c>
       <c r="H27" t="n">
-        <v>51.92</v>
+        <v>245.2823680625399</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6329,19 +6329,19 @@
         <v>1856.277345826917</v>
       </c>
       <c r="U27" t="n">
-        <v>1776.316481193986</v>
+        <v>1460.427064631128</v>
       </c>
       <c r="V27" t="n">
-        <v>1681.861261808612</v>
+        <v>1365.971845245754</v>
       </c>
       <c r="W27" t="n">
-        <v>1245.120713414846</v>
+        <v>1253.473721094412</v>
       </c>
       <c r="X27" t="n">
-        <v>821.0169361972826</v>
+        <v>1153.612368119273</v>
       </c>
       <c r="Y27" t="n">
-        <v>741.8337111809852</v>
+        <v>1074.429143102976</v>
       </c>
     </row>
     <row r="28">
@@ -6363,19 +6363,19 @@
         <v>809.1873267949505</v>
       </c>
       <c r="F28" t="n">
-        <v>855.338299386886</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G28" t="n">
-        <v>931.1543456016401</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H28" t="n">
-        <v>1027.968674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J28" t="n">
-        <v>1516.192015759408</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K28" t="n">
         <v>1615.190403564888</v>
@@ -6399,7 +6399,7 @@
         <v>463.9758216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.69634147829413</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.4524900262059</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C29" t="n">
-        <v>467.6801887706564</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D29" t="n">
-        <v>377.4386173162627</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E29" t="n">
-        <v>293.2332742790216</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F29" t="n">
-        <v>208.4962755840601</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G29" t="n">
-        <v>126.3120357733083</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6454,52 +6454,52 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>560.4418942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>1202.951894293937</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L29" t="n">
-        <v>1646.814971748371</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M29" t="n">
-        <v>1646.814971748371</v>
+        <v>2061.970205073642</v>
       </c>
       <c r="N29" t="n">
-        <v>1646.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O29" t="n">
-        <v>1809.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P29" t="n">
-        <v>2008.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S29" t="n">
-        <v>2452.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T29" t="n">
-        <v>2190.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.889943810873</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W29" t="n">
-        <v>1226.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X29" t="n">
-        <v>952.317889660934</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y29" t="n">
-        <v>760.0780586682004</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.110657215864</v>
+        <v>816.8682329734396</v>
       </c>
       <c r="C30" t="n">
         <v>776.3632709072585</v>
       </c>
       <c r="D30" t="n">
-        <v>424.91106191968</v>
+        <v>749.1534861621044</v>
       </c>
       <c r="E30" t="n">
-        <v>78.77763038239456</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F30" t="n">
         <v>59.95314317241794</v>
@@ -6563,22 +6563,22 @@
         <v>1938.448397028141</v>
       </c>
       <c r="T30" t="n">
-        <v>1856.277345826917</v>
+        <v>1532.034921584493</v>
       </c>
       <c r="U30" t="n">
-        <v>1776.316481193986</v>
+        <v>1452.074056951562</v>
       </c>
       <c r="V30" t="n">
-        <v>1681.861261808612</v>
+        <v>1357.618837566188</v>
       </c>
       <c r="W30" t="n">
-        <v>1569.36313765727</v>
+        <v>1245.120713414846</v>
       </c>
       <c r="X30" t="n">
-        <v>1469.501784682131</v>
+        <v>1145.259360439707</v>
       </c>
       <c r="Y30" t="n">
-        <v>1390.318559665834</v>
+        <v>1066.07613542341</v>
       </c>
     </row>
     <row r="31">
@@ -6642,7 +6642,7 @@
         <v>51.92</v>
       </c>
       <c r="T31" t="n">
-        <v>164.4325496506081</v>
+        <v>159.3041526995475</v>
       </c>
       <c r="U31" t="n">
         <v>327.6791351738997</v>
@@ -6685,7 +6685,7 @@
         <v>126.3120357733083</v>
       </c>
       <c r="H32" t="n">
-        <v>51.92</v>
+        <v>52.85408398404904</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
@@ -6694,22 +6694,22 @@
         <v>134.440205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>310.1117798977626</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L32" t="n">
-        <v>528.0479024103255</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M32" t="n">
-        <v>1170.557902410328</v>
+        <v>1592.039243836214</v>
       </c>
       <c r="N32" t="n">
-        <v>1646.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O32" t="n">
-        <v>1809.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P32" t="n">
-        <v>2008.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.3833844885911</v>
+        <v>492.6258087310154</v>
       </c>
       <c r="C33" t="n">
-        <v>127.87842242241</v>
+        <v>452.1208466648343</v>
       </c>
       <c r="D33" t="n">
-        <v>100.6686376772558</v>
+        <v>424.9110619196801</v>
       </c>
       <c r="E33" t="n">
-        <v>78.77763038239456</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F33" t="n">
         <v>59.95314317241794</v>
@@ -6797,25 +6797,25 @@
         <v>2071.479071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1938.448397028141</v>
+        <v>1614.205972785717</v>
       </c>
       <c r="T33" t="n">
-        <v>1856.277345826917</v>
+        <v>1347.02556120152</v>
       </c>
       <c r="U33" t="n">
-        <v>1776.316481193986</v>
+        <v>1267.064696568588</v>
       </c>
       <c r="V33" t="n">
-        <v>1357.618837566188</v>
+        <v>1172.609477183214</v>
       </c>
       <c r="W33" t="n">
-        <v>920.8782891724215</v>
+        <v>735.8689287894483</v>
       </c>
       <c r="X33" t="n">
-        <v>496.7745119548583</v>
+        <v>636.0075758143093</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.5819265555877</v>
+        <v>556.824350798012</v>
       </c>
     </row>
     <row r="34">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>443.3918839655994</v>
+        <v>439.3918839656981</v>
       </c>
       <c r="C35" t="n">
-        <v>337.8620069524742</v>
+        <v>333.8620069525729</v>
       </c>
       <c r="D35" t="n">
-        <v>271.8628597405047</v>
+        <v>267.8628597406034</v>
       </c>
       <c r="E35" t="n">
-        <v>211.8999409456879</v>
+        <v>207.8999409457865</v>
       </c>
       <c r="F35" t="n">
-        <v>151.4053664931506</v>
+        <v>147.4053664932493</v>
       </c>
       <c r="G35" t="n">
-        <v>94.17552754683497</v>
+        <v>94.09552754683695</v>
       </c>
       <c r="H35" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I35" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J35" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073644</v>
       </c>
       <c r="K35" t="n">
-        <v>683.860205073642</v>
+        <v>682.7902050736684</v>
       </c>
       <c r="L35" t="n">
-        <v>1240.240205073642</v>
+        <v>1238.180205073693</v>
       </c>
       <c r="M35" t="n">
-        <v>1330.169243836214</v>
+        <v>1793.570205073697</v>
       </c>
       <c r="N35" t="n">
-        <v>1330.169243836214</v>
+        <v>1793.570205073697</v>
       </c>
       <c r="O35" t="n">
-        <v>1493.311050093541</v>
+        <v>1956.712011331024</v>
       </c>
       <c r="P35" t="n">
-        <v>1691.62</v>
+        <v>2155.020961237483</v>
       </c>
       <c r="Q35" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R35" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="S35" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.747295098508</v>
       </c>
       <c r="T35" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233861</v>
       </c>
       <c r="U35" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538244</v>
       </c>
       <c r="V35" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.888909299028</v>
       </c>
       <c r="W35" t="n">
-        <v>999.5520648737293</v>
+        <v>995.5520648738279</v>
       </c>
       <c r="X35" t="n">
-        <v>749.7724351154791</v>
+        <v>745.7724351155778</v>
       </c>
       <c r="Y35" t="n">
-        <v>581.7750283651696</v>
+        <v>577.7750283652683</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>413.2965327542515</v>
+        <v>838.1026334425212</v>
       </c>
       <c r="C36" t="n">
-        <v>397.0339949304946</v>
+        <v>821.8400956187644</v>
       </c>
       <c r="D36" t="n">
-        <v>394.0666344277647</v>
+        <v>818.8727351160345</v>
       </c>
       <c r="E36" t="n">
-        <v>394.0666344277647</v>
+        <v>472.739303578749</v>
       </c>
       <c r="F36" t="n">
-        <v>394.0666344277647</v>
+        <v>129.6723921263481</v>
       </c>
       <c r="G36" t="n">
-        <v>394.0666344277647</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="H36" t="n">
-        <v>65.8245604639697</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I36" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J36" t="n">
-        <v>238.7276497036009</v>
+        <v>236.4581443351638</v>
       </c>
       <c r="K36" t="n">
-        <v>547.2388055149654</v>
+        <v>544.9693001465283</v>
       </c>
       <c r="L36" t="n">
-        <v>979.0274996573354</v>
+        <v>976.7579942888983</v>
       </c>
       <c r="M36" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.062386031758</v>
       </c>
       <c r="N36" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846873</v>
       </c>
       <c r="O36" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304177</v>
       </c>
       <c r="P36" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="Q36" t="n">
-        <v>2167.678747796677</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R36" t="n">
-        <v>2010.170738334202</v>
+        <v>2086.491990537623</v>
       </c>
       <c r="S36" t="n">
-        <v>1901.382487941131</v>
+        <v>1977.703740144553</v>
       </c>
       <c r="T36" t="n">
-        <v>1843.453860982331</v>
+        <v>1919.775113185753</v>
       </c>
       <c r="U36" t="n">
-        <v>1787.735420591825</v>
+        <v>1864.056672795246</v>
       </c>
       <c r="V36" t="n">
-        <v>1369.037776964026</v>
+        <v>1793.843877652296</v>
       </c>
       <c r="W36" t="n">
-        <v>932.2972285702601</v>
+        <v>1357.10332925853</v>
       </c>
       <c r="X36" t="n">
-        <v>508.1934513526969</v>
+        <v>1281.484400525815</v>
       </c>
       <c r="Y36" t="n">
-        <v>453.2526505788238</v>
+        <v>878.0587512670935</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>267.0905946885322</v>
+        <v>281.3482726483984</v>
       </c>
       <c r="C37" t="n">
-        <v>338.6426005069679</v>
+        <v>352.9002784668342</v>
       </c>
       <c r="D37" t="n">
-        <v>397.511744631968</v>
+        <v>411.7694225918342</v>
       </c>
       <c r="E37" t="n">
-        <v>460.890648843381</v>
+        <v>475.1483268032472</v>
       </c>
       <c r="F37" t="n">
-        <v>530.8016214353165</v>
+        <v>545.0592993951827</v>
       </c>
       <c r="G37" t="n">
-        <v>630.3776676500706</v>
+        <v>644.6353456099368</v>
       </c>
       <c r="H37" t="n">
-        <v>750.9519960881568</v>
+        <v>765.209674048023</v>
       </c>
       <c r="I37" t="n">
-        <v>936.2643379750593</v>
+        <v>950.5220159349255</v>
       </c>
       <c r="J37" t="n">
-        <v>1286.695337807839</v>
+        <v>1300.953015767705</v>
       </c>
       <c r="K37" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045101</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.67322831116</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296075</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532459</v>
       </c>
       <c r="R37" t="n">
-        <v>51.49391723586987</v>
+        <v>51.41391723587185</v>
       </c>
       <c r="S37" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="T37" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="U37" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="V37" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="W37" t="n">
-        <v>56.24316531901427</v>
+        <v>70.50084327888048</v>
       </c>
       <c r="X37" t="n">
-        <v>152.8239563432078</v>
+        <v>167.081634303074</v>
       </c>
       <c r="Y37" t="n">
-        <v>209.78325702224</v>
+        <v>224.0409349821063</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.1038605876113</v>
+        <v>444.0238605876133</v>
       </c>
       <c r="C38" t="n">
-        <v>338.5739835744861</v>
+        <v>338.4939835744881</v>
       </c>
       <c r="D38" t="n">
-        <v>272.5748363625166</v>
+        <v>272.4948363625186</v>
       </c>
       <c r="E38" t="n">
-        <v>212.6119175676998</v>
+        <v>212.5319175677018</v>
       </c>
       <c r="F38" t="n">
-        <v>152.1173431151626</v>
+        <v>152.0373431151646</v>
       </c>
       <c r="G38" t="n">
-        <v>94.17552754683496</v>
+        <v>94.09552754683695</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I38" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J38" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073644</v>
       </c>
       <c r="K38" t="n">
-        <v>683.860205073642</v>
+        <v>682.7902050736684</v>
       </c>
       <c r="L38" t="n">
-        <v>1240.240205073642</v>
+        <v>1238.180205073693</v>
       </c>
       <c r="M38" t="n">
-        <v>1240.240205073642</v>
+        <v>1327.159243836305</v>
       </c>
       <c r="N38" t="n">
-        <v>1330.169243836214</v>
+        <v>1882.549243836313</v>
       </c>
       <c r="O38" t="n">
-        <v>1493.311050093541</v>
+        <v>2045.69105009364</v>
       </c>
       <c r="P38" t="n">
-        <v>1691.62</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="Q38" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R38" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="S38" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.747295098508</v>
       </c>
       <c r="T38" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233861</v>
       </c>
       <c r="U38" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538244</v>
       </c>
       <c r="V38" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.888909299028</v>
       </c>
       <c r="W38" t="n">
-        <v>999.5520648737293</v>
+        <v>1000.184041495743</v>
       </c>
       <c r="X38" t="n">
-        <v>749.7724351154791</v>
+        <v>750.4044117374931</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.4870049871815</v>
+        <v>582.4070049871835</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1537.341835780655</v>
+        <v>489.6177849576727</v>
       </c>
       <c r="C39" t="n">
-        <v>1172.59444947205</v>
+        <v>396.3322089875804</v>
       </c>
       <c r="D39" t="n">
-        <v>821.1422404844714</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="E39" t="n">
-        <v>475.0088089471859</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="F39" t="n">
-        <v>131.9418974947849</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="G39" t="n">
-        <v>131.9418974947849</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="H39" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I39" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J39" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036028</v>
       </c>
       <c r="K39" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149673</v>
       </c>
       <c r="L39" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573373</v>
       </c>
       <c r="M39" t="n">
-        <v>1252.331891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N39" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846873</v>
       </c>
       <c r="O39" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304177</v>
       </c>
       <c r="P39" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="Q39" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R39" t="n">
-        <v>2088.76149590606</v>
+        <v>2086.491990537623</v>
       </c>
       <c r="S39" t="n">
-        <v>1979.973245512989</v>
+        <v>1977.703740144553</v>
       </c>
       <c r="T39" t="n">
-        <v>1922.04461855419</v>
+        <v>1919.775113185753</v>
       </c>
       <c r="U39" t="n">
-        <v>1866.326178163683</v>
+        <v>1864.056672795246</v>
       </c>
       <c r="V39" t="n">
-        <v>1796.113383020733</v>
+        <v>1445.359029167447</v>
       </c>
       <c r="W39" t="n">
-        <v>1707.857683111815</v>
+        <v>1008.618480773681</v>
       </c>
       <c r="X39" t="n">
-        <v>1632.238754379101</v>
+        <v>584.5147035561181</v>
       </c>
       <c r="Y39" t="n">
-        <v>1577.297953605228</v>
+        <v>529.573902782245</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>397.511744631968</v>
+        <v>557.2314991415578</v>
       </c>
       <c r="C40" t="n">
-        <v>397.511744631968</v>
+        <v>628.7835049599936</v>
       </c>
       <c r="D40" t="n">
-        <v>397.511744631968</v>
+        <v>687.6526490849936</v>
       </c>
       <c r="E40" t="n">
-        <v>460.890648843381</v>
+        <v>687.6526490849936</v>
       </c>
       <c r="F40" t="n">
-        <v>530.8016214353165</v>
+        <v>687.6526490849936</v>
       </c>
       <c r="G40" t="n">
-        <v>630.3776676500706</v>
+        <v>687.6526490849936</v>
       </c>
       <c r="H40" t="n">
-        <v>750.9519960881568</v>
+        <v>765.209674048023</v>
       </c>
       <c r="I40" t="n">
-        <v>936.2643379750593</v>
+        <v>950.5220159349255</v>
       </c>
       <c r="J40" t="n">
-        <v>1286.695337807839</v>
+        <v>1300.953015767705</v>
       </c>
       <c r="K40" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045101</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.67322831116</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296075</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.5309731532439</v>
+        <v>408.4509731532459</v>
       </c>
       <c r="R40" t="n">
-        <v>51.49391723586989</v>
+        <v>51.41391723587185</v>
       </c>
       <c r="S40" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="T40" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="U40" t="n">
-        <v>373.3675321249603</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="V40" t="n">
-        <v>373.3675321249603</v>
+        <v>325.5239425365561</v>
       </c>
       <c r="W40" t="n">
-        <v>373.3675321249603</v>
+        <v>442.9648607962335</v>
       </c>
       <c r="X40" t="n">
-        <v>373.3675321249603</v>
+        <v>442.9648607962335</v>
       </c>
       <c r="Y40" t="n">
-        <v>373.3675321249603</v>
+        <v>499.9241614752657</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.1038605876113</v>
+        <v>444.0238605876133</v>
       </c>
       <c r="C41" t="n">
-        <v>338.5739835744861</v>
+        <v>338.4939835744881</v>
       </c>
       <c r="D41" t="n">
-        <v>272.5748363625166</v>
+        <v>272.4948363625186</v>
       </c>
       <c r="E41" t="n">
-        <v>212.6119175676998</v>
+        <v>212.5319175677018</v>
       </c>
       <c r="F41" t="n">
-        <v>152.1173431151626</v>
+        <v>152.0373431151646</v>
       </c>
       <c r="G41" t="n">
-        <v>94.17552754683497</v>
+        <v>94.09552754683695</v>
       </c>
       <c r="H41" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I41" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J41" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073644</v>
       </c>
       <c r="K41" t="n">
-        <v>683.860205073642</v>
+        <v>553.8331213237338</v>
       </c>
       <c r="L41" t="n">
-        <v>1240.240205073642</v>
+        <v>771.7692438362966</v>
       </c>
       <c r="M41" t="n">
-        <v>1796.620205073642</v>
+        <v>771.7692438362966</v>
       </c>
       <c r="N41" t="n">
-        <v>1886.549243836214</v>
+        <v>1327.159243836305</v>
       </c>
       <c r="O41" t="n">
-        <v>2049.691050093541</v>
+        <v>1490.301050093632</v>
       </c>
       <c r="P41" t="n">
-        <v>2248</v>
+        <v>1688.610000000091</v>
       </c>
       <c r="Q41" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R41" t="n">
-        <v>2248</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="S41" t="n">
-        <v>2129.459271720421</v>
+        <v>2124.747295098508</v>
       </c>
       <c r="T41" t="n">
-        <v>1891.510706855774</v>
+        <v>1886.798730233861</v>
       </c>
       <c r="U41" t="n">
-        <v>1584.329193160157</v>
+        <v>1579.617216538244</v>
       </c>
       <c r="V41" t="n">
-        <v>1296.600885920941</v>
+        <v>1291.888909299028</v>
       </c>
       <c r="W41" t="n">
-        <v>1000.264041495741</v>
+        <v>1000.184041495743</v>
       </c>
       <c r="X41" t="n">
-        <v>750.484411737491</v>
+        <v>750.4044117374931</v>
       </c>
       <c r="Y41" t="n">
-        <v>582.4870049871815</v>
+        <v>582.4070049871835</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>143.4024418412611</v>
+        <v>1101.795089801024</v>
       </c>
       <c r="C42" t="n">
-        <v>127.1399040175043</v>
+        <v>1085.532551977267</v>
       </c>
       <c r="D42" t="n">
-        <v>44.96</v>
+        <v>734.0803429896885</v>
       </c>
       <c r="E42" t="n">
-        <v>44.96</v>
+        <v>387.9469114524029</v>
       </c>
       <c r="F42" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="G42" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="H42" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I42" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J42" t="n">
-        <v>238.7276497036009</v>
+        <v>236.4581443351638</v>
       </c>
       <c r="K42" t="n">
-        <v>547.2388055149654</v>
+        <v>544.9693001465283</v>
       </c>
       <c r="L42" t="n">
-        <v>979.0274996573354</v>
+        <v>976.7579942888983</v>
       </c>
       <c r="M42" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.062386031758</v>
       </c>
       <c r="N42" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846873</v>
       </c>
       <c r="O42" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304177</v>
       </c>
       <c r="P42" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="Q42" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000099</v>
       </c>
       <c r="R42" t="n">
-        <v>2088.76149590606</v>
+        <v>2086.491990537623</v>
       </c>
       <c r="S42" t="n">
-        <v>1979.973245512989</v>
+        <v>1977.703740144553</v>
       </c>
       <c r="T42" t="n">
-        <v>1922.04461855419</v>
+        <v>1834.982721059407</v>
       </c>
       <c r="U42" t="n">
-        <v>1866.326178163683</v>
+        <v>1430.779432184051</v>
       </c>
       <c r="V42" t="n">
-        <v>1796.113383020733</v>
+        <v>1360.566637041102</v>
       </c>
       <c r="W42" t="n">
-        <v>1359.372834626967</v>
+        <v>1272.310937132184</v>
       </c>
       <c r="X42" t="n">
-        <v>935.2690574094036</v>
+        <v>1196.692008399469</v>
       </c>
       <c r="Y42" t="n">
-        <v>531.843408150682</v>
+        <v>1141.751207625596</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>381.0043188631504</v>
+        <v>267.0105946885343</v>
       </c>
       <c r="C43" t="n">
-        <v>452.5563246815861</v>
+        <v>338.5626005069701</v>
       </c>
       <c r="D43" t="n">
-        <v>511.4254688065863</v>
+        <v>397.4317446319701</v>
       </c>
       <c r="E43" t="n">
-        <v>574.8043730179993</v>
+        <v>460.8106488433831</v>
       </c>
       <c r="F43" t="n">
-        <v>644.7153456099347</v>
+        <v>530.7216214353186</v>
       </c>
       <c r="G43" t="n">
-        <v>644.7153456099347</v>
+        <v>630.2976676500728</v>
       </c>
       <c r="H43" t="n">
-        <v>765.2896740480209</v>
+        <v>750.8719960881589</v>
       </c>
       <c r="I43" t="n">
-        <v>950.6020159349234</v>
+        <v>936.1843379750615</v>
       </c>
       <c r="J43" t="n">
-        <v>1301.033015767703</v>
+        <v>1286.615337807841</v>
       </c>
       <c r="K43" t="n">
-        <v>1428.919800524243</v>
+        <v>1414.502122564381</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045101</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.67322831116</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296075</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532459</v>
       </c>
       <c r="R43" t="n">
-        <v>51.49391723586987</v>
+        <v>51.41391723587185</v>
       </c>
       <c r="S43" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="T43" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="U43" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="V43" t="n">
-        <v>323.6969811968582</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="W43" t="n">
-        <v>323.6969811968582</v>
+        <v>181.1525496506101</v>
       </c>
       <c r="X43" t="n">
-        <v>323.6969811968582</v>
+        <v>209.7032570222422</v>
       </c>
       <c r="Y43" t="n">
-        <v>323.6969811968582</v>
+        <v>209.7032570222422</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>443.3918839655994</v>
+        <v>439.3918839656908</v>
       </c>
       <c r="C44" t="n">
-        <v>337.8620069524742</v>
+        <v>333.8620069525656</v>
       </c>
       <c r="D44" t="n">
-        <v>271.8628597405047</v>
+        <v>267.8628597405961</v>
       </c>
       <c r="E44" t="n">
-        <v>211.8999409456879</v>
+        <v>207.8999409457793</v>
       </c>
       <c r="F44" t="n">
-        <v>151.4053664931506</v>
+        <v>147.405366493242</v>
       </c>
       <c r="G44" t="n">
-        <v>93.46355092482301</v>
+        <v>94.09552754683693</v>
       </c>
       <c r="H44" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I44" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J44" t="n">
-        <v>553.4818942939371</v>
+        <v>553.4018942939391</v>
       </c>
       <c r="K44" t="n">
-        <v>773.7892438362142</v>
+        <v>1108.791894293963</v>
       </c>
       <c r="L44" t="n">
-        <v>1330.169243836214</v>
+        <v>1327.159243836299</v>
       </c>
       <c r="M44" t="n">
-        <v>1330.169243836214</v>
+        <v>1327.159243836299</v>
       </c>
       <c r="N44" t="n">
-        <v>1330.169243836214</v>
+        <v>1327.159243836299</v>
       </c>
       <c r="O44" t="n">
-        <v>1493.311050093541</v>
+        <v>1490.301050093626</v>
       </c>
       <c r="P44" t="n">
-        <v>1691.62</v>
+        <v>1688.610000000085</v>
       </c>
       <c r="Q44" t="n">
-        <v>2248</v>
+        <v>2244.000000000091</v>
       </c>
       <c r="R44" t="n">
-        <v>2248</v>
+        <v>2244.000000000091</v>
       </c>
       <c r="S44" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.747295098501</v>
       </c>
       <c r="T44" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233854</v>
       </c>
       <c r="U44" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538236</v>
       </c>
       <c r="V44" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.88890929902</v>
       </c>
       <c r="W44" t="n">
-        <v>999.5520648737293</v>
+        <v>995.5520648738207</v>
       </c>
       <c r="X44" t="n">
-        <v>749.7724351154791</v>
+        <v>745.7724351155705</v>
       </c>
       <c r="Y44" t="n">
-        <v>581.7750283651696</v>
+        <v>577.7750283652611</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1188.856987295807</v>
+        <v>141.1329364728172</v>
       </c>
       <c r="C45" t="n">
-        <v>824.1096009872012</v>
+        <v>124.8703986490603</v>
       </c>
       <c r="D45" t="n">
-        <v>821.1422404844714</v>
+        <v>121.9030381463304</v>
       </c>
       <c r="E45" t="n">
-        <v>475.0088089471859</v>
+        <v>121.9030381463304</v>
       </c>
       <c r="F45" t="n">
-        <v>475.0088089471859</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="G45" t="n">
-        <v>146.7328912537143</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="H45" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="I45" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="J45" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036028</v>
       </c>
       <c r="K45" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149673</v>
       </c>
       <c r="L45" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573373</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.06238603175</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846866</v>
       </c>
       <c r="O45" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.37056930417</v>
       </c>
       <c r="P45" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000091</v>
       </c>
       <c r="Q45" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000091</v>
       </c>
       <c r="R45" t="n">
-        <v>2088.76149590606</v>
+        <v>1738.007142052767</v>
       </c>
       <c r="S45" t="n">
-        <v>1979.973245512989</v>
+        <v>1280.734043174848</v>
       </c>
       <c r="T45" t="n">
-        <v>1922.04461855419</v>
+        <v>874.3205677312001</v>
       </c>
       <c r="U45" t="n">
-        <v>1866.326178163683</v>
+        <v>818.6021273406932</v>
       </c>
       <c r="V45" t="n">
-        <v>1796.113383020733</v>
+        <v>399.904483712895</v>
       </c>
       <c r="W45" t="n">
-        <v>1707.857683111815</v>
+        <v>311.6487838039773</v>
       </c>
       <c r="X45" t="n">
-        <v>1632.238754379101</v>
+        <v>236.0298550712626</v>
       </c>
       <c r="Y45" t="n">
-        <v>1228.813105120379</v>
+        <v>181.0890542973895</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>344.8071768598093</v>
+        <v>267.0105946885341</v>
       </c>
       <c r="C46" t="n">
-        <v>416.359182678245</v>
+        <v>338.5626005069698</v>
       </c>
       <c r="D46" t="n">
-        <v>475.2283268032451</v>
+        <v>397.4317446319699</v>
       </c>
       <c r="E46" t="n">
-        <v>475.2283268032451</v>
+        <v>460.8106488433829</v>
       </c>
       <c r="F46" t="n">
-        <v>545.1392993951806</v>
+        <v>530.7216214353184</v>
       </c>
       <c r="G46" t="n">
-        <v>644.7153456099347</v>
+        <v>630.2976676500725</v>
       </c>
       <c r="H46" t="n">
-        <v>765.2896740480209</v>
+        <v>750.8719960881587</v>
       </c>
       <c r="I46" t="n">
-        <v>950.6020159349234</v>
+        <v>936.1843379750612</v>
       </c>
       <c r="J46" t="n">
-        <v>1301.033015767703</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K46" t="n">
-        <v>1428.919800524243</v>
+        <v>1414.502122564381</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.5121420451</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311159</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296074</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532459</v>
       </c>
       <c r="R46" t="n">
-        <v>51.49391723586987</v>
+        <v>51.41391723587186</v>
       </c>
       <c r="S46" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="T46" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="U46" t="n">
-        <v>44.96</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="V46" t="n">
-        <v>73.4781299096462</v>
+        <v>44.88000000000198</v>
       </c>
       <c r="W46" t="n">
-        <v>190.9190481693236</v>
+        <v>113.4705029853083</v>
       </c>
       <c r="X46" t="n">
-        <v>287.4998391935171</v>
+        <v>210.0512940095018</v>
       </c>
       <c r="Y46" t="n">
-        <v>287.4998391935171</v>
+        <v>267.0105946885341</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>242.0199542155221</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>234.2887077235403</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748743</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="M5" t="n">
-        <v>772.4711016975159</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748743</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N8" t="n">
-        <v>704.2928768486519</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>427.7398593877089</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>471.5539648241206</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L11" t="n">
-        <v>428.8625025125627</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M11" t="n">
-        <v>692.3342705229481</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N11" t="n">
-        <v>228.3401037984784</v>
+        <v>619.3980326290609</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,13 +8915,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>267.9409117477912</v>
       </c>
       <c r="L14" t="n">
-        <v>50.76301021994982</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M14" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N14" t="n">
         <v>228.3401037984784</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>267.9409117477912</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M17" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N17" t="n">
-        <v>872.7740959253404</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>251.0750808325347</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M20" t="n">
-        <v>299.3167457327696</v>
+        <v>472.679411149509</v>
       </c>
       <c r="N20" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984784</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>448.6879293874151</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M23" t="n">
-        <v>780.3844925388761</v>
+        <v>472.6794111495062</v>
       </c>
       <c r="N23" t="n">
-        <v>877.3401037984784</v>
+        <v>876.3401037984811</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9869,10 +9869,10 @@
         <v>428.8625025125627</v>
       </c>
       <c r="M26" t="n">
-        <v>948.3167457327718</v>
+        <v>473.6390071091047</v>
       </c>
       <c r="N26" t="n">
-        <v>402.6623651748116</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>471.5539648241206</v>
       </c>
       <c r="L29" t="n">
-        <v>228.2090453958292</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M29" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N29" t="n">
-        <v>228.3401037984784</v>
+        <v>402.6623651748134</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M32" t="n">
-        <v>948.3167457327718</v>
+        <v>473.6390071091047</v>
       </c>
       <c r="N32" t="n">
-        <v>709.4078506045828</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>384.5539648241206</v>
+        <v>383.5539648241453</v>
       </c>
       <c r="L35" t="n">
-        <v>341.862502512563</v>
+        <v>340.8625025125873</v>
       </c>
       <c r="M35" t="n">
-        <v>390.1541586242564</v>
+        <v>860.3167457327743</v>
       </c>
       <c r="N35" t="n">
         <v>228.3401037984784</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>584.1810913626613</v>
+        <v>112.058908294596</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>225.2531203435066</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>384.5539648241206</v>
+        <v>383.5539648241453</v>
       </c>
       <c r="L38" t="n">
-        <v>341.862502512563</v>
+        <v>340.8625025125873</v>
       </c>
       <c r="M38" t="n">
-        <v>299.3167457327696</v>
+        <v>389.1945626647008</v>
       </c>
       <c r="N38" t="n">
-        <v>319.1775166899653</v>
+        <v>789.3401037984866</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>584.1810913626613</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10899,7 +10899,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870686</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>384.5539648241206</v>
+        <v>253.2942842686558</v>
       </c>
       <c r="L41" t="n">
-        <v>341.862502512563</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>861.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N41" t="n">
-        <v>319.1775166899655</v>
+        <v>789.3401037984866</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22.18109136266131</v>
+        <v>583.1810913626696</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>225.2531203435066</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11285,10 +11285,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>45.08664112945098</v>
+        <v>383.5539648241452</v>
       </c>
       <c r="L44" t="n">
-        <v>341.8625025125628</v>
+        <v>0.4355828583563834</v>
       </c>
       <c r="M44" t="n">
         <v>299.3167457327696</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>584.1810913626613</v>
+        <v>583.1810913626678</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11370,7 +11370,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>469.4831988458184</v>
       </c>
       <c r="N45" t="n">
         <v>485.4085271713503</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.717292974490192e-12</v>
+        <v>8.292651889836218e-13</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.956056855791644</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23469,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2.956056855791473</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.956056855777675</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23997,7 +23997,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.956056855791644</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.95605685579163</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.704856855791842</v>
+        <v>4.585656855696104</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25419,13 +25419,13 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.585656855696129</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.7048568557918031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.7048568557913342</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25656,7 +25656,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>4.585656855696129</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25845,10 +25845,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.58565685570327</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7048568557918315</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>853738.030650863</v>
+        <v>853628.188650863</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1609364.254850419</v>
+        <v>1609254.412850419</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2364990.479049976</v>
+        <v>2364880.637049976</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3119708.079916201</v>
+        <v>3119472.343489253</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3875334.304115758</v>
+        <v>3874957.386413378</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4630960.528315314</v>
+        <v>4630442.429337502</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5386586.752514868</v>
+        <v>5385927.472261623</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6142212.976714422</v>
+        <v>6141412.515185745</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6897839.200913976</v>
+        <v>6897133.294536814</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7653465.42511353</v>
+        <v>7652759.518736368</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8409091.649313089</v>
+        <v>8408385.742935926</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9156457.9113674</v>
+        <v>9155443.971004177</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9912050.47160353</v>
+        <v>9910851.184232311</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10667643.03183966</v>
+        <v>10666258.39746045</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11423235.59207579</v>
+        <v>11421665.61068858</v>
       </c>
     </row>
   </sheetData>
@@ -26278,40 +26278,40 @@
         <v>1448283.596382485</v>
       </c>
       <c r="E2" t="n">
+        <v>1448012.998937905</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1448012.998937905</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1448012.998937906</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1448012.998937905</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1448012.998937905</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1448283.596382483</v>
+      </c>
+      <c r="K2" t="n">
         <v>1448283.596382484</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1448283.596382484</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1448283.596382484</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1448283.596382485</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1448283.596382484</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1448283.596382484</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1448283.596382485</v>
       </c>
       <c r="L2" t="n">
         <v>1448283.596382484</v>
       </c>
       <c r="M2" t="n">
-        <v>1448219.073785906</v>
+        <v>1447863.825353914</v>
       </c>
       <c r="N2" t="n">
-        <v>1448219.073785905</v>
+        <v>1447863.825353914</v>
       </c>
       <c r="O2" t="n">
-        <v>1448219.073785905</v>
+        <v>1447863.825353914</v>
       </c>
       <c r="P2" t="n">
-        <v>1448219.073785906</v>
+        <v>1447863.825353914</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>592475</v>
+        <v>591148</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85376</v>
+        <v>84672.00000000869</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.606606806</v>
+        <v>597948.3132650449</v>
       </c>
       <c r="E4" t="n">
-        <v>514005.3727838712</v>
+        <v>513751.7523916513</v>
       </c>
       <c r="F4" t="n">
-        <v>512320.9448683569</v>
+        <v>512067.1546396873</v>
       </c>
       <c r="G4" t="n">
-        <v>510634.1925055168</v>
+        <v>510380.23220603</v>
       </c>
       <c r="H4" t="n">
-        <v>508945.0990266501</v>
+        <v>508690.9684202963</v>
       </c>
       <c r="I4" t="n">
-        <v>507253.6475458712</v>
+        <v>506999.3463948999</v>
       </c>
       <c r="J4" t="n">
-        <v>505559.8209559915</v>
+        <v>505362.3521738977</v>
       </c>
       <c r="K4" t="n">
-        <v>503863.6019243026</v>
+        <v>503666.133142209</v>
       </c>
       <c r="L4" t="n">
-        <v>502164.9728882493</v>
+        <v>501967.5041061556</v>
       </c>
       <c r="M4" t="n">
-        <v>506566.2673210927</v>
+        <v>506308.9084534692</v>
       </c>
       <c r="N4" t="n">
-        <v>504800.3868513845</v>
+        <v>504542.8135297517</v>
       </c>
       <c r="O4" t="n">
-        <v>503031.9520361847</v>
+        <v>502774.1639503349</v>
       </c>
       <c r="P4" t="n">
-        <v>501260.9436696268</v>
+        <v>501002.9405070199</v>
       </c>
     </row>
     <row r="5">
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="F5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="G5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="H5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="I5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="J5" t="n">
         <v>74009.94899999999</v>
@@ -26458,16 +26458,16 @@
         <v>74009.94899999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70738.005</v>
+        <v>70677.2050000015</v>
       </c>
       <c r="N5" t="n">
-        <v>70738.005</v>
+        <v>70677.2050000015</v>
       </c>
       <c r="O5" t="n">
-        <v>70738.005</v>
+        <v>70677.2050000015</v>
       </c>
       <c r="P5" t="n">
-        <v>70738.005</v>
+        <v>70677.2050000015</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>556176.0201723657</v>
+        <v>555630.6305310298</v>
       </c>
       <c r="C6" t="n">
-        <v>789282.9423598546</v>
+        <v>789711.9945886366</v>
       </c>
       <c r="D6" t="n">
-        <v>791294.5897756785</v>
+        <v>791723.0831174396</v>
       </c>
       <c r="E6" t="n">
-        <v>267793.2745986129</v>
+        <v>269164.0975462541</v>
       </c>
       <c r="F6" t="n">
-        <v>861952.7025141271</v>
+        <v>861996.6952982176</v>
       </c>
       <c r="G6" t="n">
-        <v>863639.454876967</v>
+        <v>863683.6177318764</v>
       </c>
       <c r="H6" t="n">
-        <v>865328.5483558344</v>
+        <v>865372.8815176088</v>
       </c>
       <c r="I6" t="n">
-        <v>867019.9998366124</v>
+        <v>867064.5035430047</v>
       </c>
       <c r="J6" t="n">
-        <v>480265.8264264925</v>
+        <v>480111.2952085854</v>
       </c>
       <c r="K6" t="n">
-        <v>870410.0454581819</v>
+        <v>870607.5142402751</v>
       </c>
       <c r="L6" t="n">
-        <v>872108.6744942345</v>
+        <v>872306.1432763282</v>
       </c>
       <c r="M6" t="n">
-        <v>785538.8014648129</v>
+        <v>786205.7119004347</v>
       </c>
       <c r="N6" t="n">
-        <v>872680.681934521</v>
+        <v>872643.8068241607</v>
       </c>
       <c r="O6" t="n">
-        <v>617649.1167497208</v>
+        <v>617612.4564035776</v>
       </c>
       <c r="P6" t="n">
-        <v>876220.125116279</v>
+        <v>876183.6798468924</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>347</v>
@@ -26868,19 +26868,19 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J4" t="n">
         <v>649</v>
@@ -26892,16 +26892,16 @@
         <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
       <c r="N4" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
       <c r="O4" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
       <c r="P4" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>188</v>
+        <v>186.0000000000176</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27451,40 +27451,40 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
+        <v>398.0465935392077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>134.1177124465037</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>224.8682520946261</v>
+      </c>
+      <c r="S2" t="n">
         <v>400</v>
-      </c>
-      <c r="I2" t="n">
-        <v>134.2726973711268</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>225.120779732817</v>
-      </c>
-      <c r="S2" t="n">
-        <v>398.2013121321719</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27563,25 +27563,25 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
+        <v>88.44885845517734</v>
+      </c>
+      <c r="T3" t="n">
         <v>400</v>
       </c>
-      <c r="T3" t="n">
-        <v>30.47344446279683</v>
-      </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>26.19578428848864</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>255.8059973915321</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>316.6875110528767</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27603,25 +27603,25 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H4" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>396.1372930982029</v>
+      </c>
+      <c r="K4" t="n">
         <v>400</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
         <v>400</v>
-      </c>
-      <c r="I4" t="n">
-        <v>171.1020457840527</v>
-      </c>
-      <c r="J4" t="n">
-        <v>396.2647849014816</v>
-      </c>
-      <c r="K4" t="n">
-        <v>267.1509377355693</v>
-      </c>
-      <c r="L4" t="n">
-        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>340.4697271893201</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>347.6483414931795</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27758,16 +27758,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>259.9683808848158</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,13 +27809,13 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>290.6375857693747</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27834,31 +27834,31 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>342.0400961869587</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>296.8535634081464</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27992,22 +27992,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,13 +28034,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>394.6389026985112</v>
+        <v>159.5184388018133</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>310.6051133171162</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>30.46477465147608</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>350.3135087567612</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
+        <v>171.047816275856</v>
+      </c>
+      <c r="J10" t="n">
+        <v>396.1372930982029</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="J10" t="n">
-        <v>396.2647849014816</v>
-      </c>
-      <c r="K10" t="n">
-        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28131,7 +28131,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>258.8042224726964</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28223,19 +28223,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28274,7 +28274,7 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28289,7 +28289,7 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28314,7 +28314,7 @@
         <v>321</v>
       </c>
       <c r="F13" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="G13" t="n">
         <v>321</v>
@@ -28356,7 +28356,7 @@
         <v>321</v>
       </c>
       <c r="T13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="U13" t="n">
         <v>321</v>
@@ -28447,7 +28447,7 @@
         <v>321</v>
       </c>
       <c r="X14" t="n">
-        <v>320.0752568557917</v>
+        <v>321</v>
       </c>
       <c r="Y14" t="n">
         <v>321</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
@@ -28481,7 +28481,7 @@
         <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>191.4287443819146</v>
+        <v>8.269477602770934</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R15" t="n">
-        <v>137.8407332208566</v>
+        <v>321</v>
       </c>
       <c r="S15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28557,46 +28557,46 @@
         <v>321</v>
       </c>
       <c r="H16" t="n">
+        <v>321</v>
+      </c>
+      <c r="I16" t="n">
+        <v>321</v>
+      </c>
+      <c r="J16" t="n">
+        <v>321</v>
+      </c>
+      <c r="K16" t="n">
+        <v>321</v>
+      </c>
+      <c r="L16" t="n">
+        <v>321</v>
+      </c>
+      <c r="M16" t="n">
+        <v>321</v>
+      </c>
+      <c r="N16" t="n">
+        <v>321</v>
+      </c>
+      <c r="O16" t="n">
+        <v>321</v>
+      </c>
+      <c r="P16" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>321</v>
+      </c>
+      <c r="R16" t="n">
+        <v>321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>321</v>
+      </c>
+      <c r="T16" t="n">
+        <v>321</v>
+      </c>
+      <c r="U16" t="n">
         <v>315.8198010595348</v>
-      </c>
-      <c r="I16" t="n">
-        <v>321</v>
-      </c>
-      <c r="J16" t="n">
-        <v>321</v>
-      </c>
-      <c r="K16" t="n">
-        <v>321</v>
-      </c>
-      <c r="L16" t="n">
-        <v>321</v>
-      </c>
-      <c r="M16" t="n">
-        <v>321</v>
-      </c>
-      <c r="N16" t="n">
-        <v>321</v>
-      </c>
-      <c r="O16" t="n">
-        <v>321</v>
-      </c>
-      <c r="P16" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>321</v>
-      </c>
-      <c r="R16" t="n">
-        <v>321</v>
-      </c>
-      <c r="S16" t="n">
-        <v>321</v>
-      </c>
-      <c r="T16" t="n">
-        <v>321</v>
-      </c>
-      <c r="U16" t="n">
-        <v>321</v>
       </c>
       <c r="V16" t="n">
         <v>321</v>
@@ -28666,10 +28666,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760474</v>
       </c>
       <c r="S17" t="n">
-        <v>320.0752568557917</v>
+        <v>321</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>215.6455832169962</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R18" t="n">
         <v>321</v>
@@ -28754,13 +28754,13 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
@@ -28791,7 +28791,7 @@
         <v>321</v>
       </c>
       <c r="G19" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="H19" t="n">
         <v>321</v>
@@ -28833,7 +28833,7 @@
         <v>321</v>
       </c>
       <c r="U19" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="V19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28937,7 +28937,7 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -28955,7 +28955,7 @@
         <v>321</v>
       </c>
       <c r="I21" t="n">
-        <v>191.4287443819146</v>
+        <v>8.269477602770991</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29028,7 +29028,7 @@
         <v>321</v>
       </c>
       <c r="G22" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="H22" t="n">
         <v>321</v>
@@ -29082,7 +29082,7 @@
         <v>321</v>
       </c>
       <c r="Y22" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="23">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,13 +29174,13 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29271,10 +29271,10 @@
         <v>321</v>
       </c>
       <c r="I25" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="J25" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K25" t="n">
         <v>321</v>
@@ -29347,10 +29347,10 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>321</v>
+        <v>320.0752568557915</v>
       </c>
       <c r="I26" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,19 +29408,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>137.8407332208564</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
@@ -29429,7 +29429,7 @@
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,16 +29465,16 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>8.269477602770735</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29499,7 +29499,7 @@
         <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="G28" t="n">
         <v>321</v>
@@ -29514,7 +29514,7 @@
         <v>321</v>
       </c>
       <c r="K28" t="n">
-        <v>315.8198010595346</v>
+        <v>321</v>
       </c>
       <c r="L28" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320.0752568557915</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
         <v>96.3013908384635</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137.8407332208564</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29699,7 +29699,7 @@
         <v>321</v>
       </c>
       <c r="T30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>321</v>
@@ -29778,10 +29778,10 @@
         <v>321</v>
       </c>
       <c r="T31" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="U31" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V31" t="n">
         <v>321</v>
@@ -29821,10 +29821,10 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.0752568557915</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3013908384635</v>
+        <v>95.37664769425496</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29894,7 +29894,7 @@
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29933,25 +29933,25 @@
         <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -30128,19 +30128,19 @@
         <v>345</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9931585165368</v>
+        <v>241.0486903114541</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>170.7728295225845</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R36" t="n">
         <v>345</v>
@@ -30179,16 +30179,16 @@
         <v>345</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30228,7 +30228,7 @@
         <v>345</v>
       </c>
       <c r="L37" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M37" t="n">
         <v>345</v>
@@ -30261,7 +30261,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>237.7699465245827</v>
+        <v>252.2524495143445</v>
       </c>
       <c r="X37" t="n">
         <v>345</v>
@@ -30359,22 +30359,22 @@
         <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>268.747192235128</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>324.9931585165368</v>
       </c>
       <c r="H39" t="n">
-        <v>238.8475747043199</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
         <v>191.4287443819146</v>
@@ -30416,13 +30416,13 @@
         <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>345</v>
@@ -30435,25 +30435,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>311.5018937785005</v>
+        <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E40" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>345</v>
+        <v>244.418135136612</v>
       </c>
       <c r="H40" t="n">
-        <v>345</v>
+        <v>301.5481783080235</v>
       </c>
       <c r="I40" t="n">
         <v>345</v>
@@ -30465,7 +30465,7 @@
         <v>345</v>
       </c>
       <c r="L40" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M40" t="n">
         <v>345</v>
@@ -30492,19 +30492,19 @@
         <v>345</v>
       </c>
       <c r="U40" t="n">
+        <v>150.9242601269169</v>
+      </c>
+      <c r="V40" t="n">
         <v>345</v>
       </c>
-      <c r="V40" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41">
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C42" t="n">
         <v>345</v>
       </c>
       <c r="D42" t="n">
-        <v>266.5795819203734</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>324.9931585165368</v>
@@ -30647,22 +30647,22 @@
         <v>345</v>
       </c>
       <c r="T42" t="n">
-        <v>345</v>
+        <v>261.0555317949176</v>
       </c>
       <c r="U42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>345</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43">
@@ -30687,7 +30687,7 @@
         <v>345</v>
       </c>
       <c r="G43" t="n">
-        <v>244.418135136612</v>
+        <v>345</v>
       </c>
       <c r="H43" t="n">
         <v>345</v>
@@ -30702,7 +30702,7 @@
         <v>345</v>
       </c>
       <c r="L43" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30732,13 +30732,13 @@
         <v>150.9242601269169</v>
       </c>
       <c r="V43" t="n">
-        <v>343.0737764245496</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X43" t="n">
-        <v>247.4436454301076</v>
+        <v>276.2827437852914</v>
       </c>
       <c r="Y43" t="n">
         <v>287.4653528494624</v>
@@ -30833,22 +30833,22 @@
         <v>345</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D45" t="n">
         <v>345</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>263.3834345730118</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H45" t="n">
-        <v>224.2044908829798</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
         <v>191.4287443819146</v>
@@ -30878,19 +30878,19 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>345</v>
       </c>
       <c r="V45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>345</v>
@@ -30899,7 +30899,7 @@
         <v>345</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46">
@@ -30909,7 +30909,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C46" t="n">
         <v>345</v>
@@ -30918,7 +30918,7 @@
         <v>345</v>
       </c>
       <c r="E46" t="n">
-        <v>280.9809048369565</v>
+        <v>345</v>
       </c>
       <c r="F46" t="n">
         <v>345</v>
@@ -30939,7 +30939,7 @@
         <v>345</v>
       </c>
       <c r="L46" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30969,16 +30969,16 @@
         <v>150.9242601269169</v>
       </c>
       <c r="V46" t="n">
-        <v>227.9765020441417</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W46" t="n">
-        <v>345</v>
+        <v>295.656146187504</v>
       </c>
       <c r="X46" t="n">
         <v>345</v>
       </c>
       <c r="Y46" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34746,10 +34746,10 @@
         <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>294.1798838637633</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>299.6321147587162</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -34758,13 +34758,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>59.25677413017286</v>
+      </c>
+      <c r="Q2" t="n">
         <v>374</v>
-      </c>
-      <c r="P2" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34889,25 +34889,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648883</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>189.5213687017473</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>148.4780312769633</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,16 +34980,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>373.9999999999999</v>
+        <v>299.5314174862184</v>
       </c>
       <c r="M5" t="n">
-        <v>300.2102102361031</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -34998,7 +34998,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
         <v>374</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35120,31 +35120,31 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>56.50387813140321</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>29.70262567257716</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35168,19 +35168,19 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="L8" t="n">
         <v>374</v>
       </c>
-      <c r="L8" t="n">
-        <v>373.9999999999999</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>300.2102102361031</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>299.6321147587159</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,31 +35357,31 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>75.93065278901928</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35417,7 +35417,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>11.36057704258885</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,16 +35457,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K11" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L11" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M11" t="n">
-        <v>393.0175247901786</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>391.0579288305826</v>
       </c>
       <c r="O11" t="n">
         <v>164.7897032902292</v>
@@ -35600,7 +35600,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F13" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G13" t="n">
         <v>76.58186486338801</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U13" t="n">
         <v>170.0757398730831</v>
@@ -35694,13 +35694,13 @@
         <v>513.658479084785</v>
       </c>
       <c r="K14" t="n">
-        <v>177.4460351758794</v>
+        <v>445.3869469236706</v>
       </c>
       <c r="L14" t="n">
-        <v>270.9005077073871</v>
+        <v>648</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         <v>76.58186486338801</v>
       </c>
       <c r="H16" t="n">
-        <v>92.61205200709649</v>
+        <v>97.79225094756171</v>
       </c>
       <c r="I16" t="n">
         <v>163.184183724144</v>
@@ -35882,7 +35882,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U16" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326179</v>
       </c>
       <c r="V16" t="n">
         <v>121.8296897837838</v>
@@ -35931,16 +35931,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K17" t="n">
-        <v>177.4460351758794</v>
+        <v>445.3869469236706</v>
       </c>
       <c r="L17" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>644.4339921268619</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
@@ -35949,10 +35949,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.423956351260645e-11</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36077,7 +36077,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>71.40166592292275</v>
+        <v>76.58186486338801</v>
       </c>
       <c r="H19" t="n">
         <v>97.79225094756171</v>
@@ -36119,7 +36119,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U19" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326179</v>
       </c>
       <c r="V19" t="n">
         <v>121.8296897837838</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K20" t="n">
-        <v>428.5211160084141</v>
+        <v>648</v>
       </c>
       <c r="L20" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>173.3626654167394</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P20" t="n">
-        <v>649</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36314,7 +36314,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>71.40166592292275</v>
+        <v>76.58186486338801</v>
       </c>
       <c r="H22" t="n">
         <v>97.79225094756171</v>
@@ -36368,7 +36368,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="23">
@@ -36405,16 +36405,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K23" t="n">
-        <v>177.4460351758794</v>
+        <v>648</v>
       </c>
       <c r="L23" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M23" t="n">
-        <v>481.0677468061065</v>
+        <v>173.3626654167367</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>648.0000000000026</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36423,7 +36423,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36557,10 +36557,10 @@
         <v>97.79225094756171</v>
       </c>
       <c r="I25" t="n">
-        <v>163.184183724144</v>
+        <v>158.0039847836788</v>
       </c>
       <c r="J25" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K25" t="n">
         <v>105.178570461152</v>
@@ -36648,10 +36648,10 @@
         <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>649.0000000000022</v>
+        <v>174.3222613763352</v>
       </c>
       <c r="N26" t="n">
-        <v>174.3222613763331</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
@@ -36785,7 +36785,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G28" t="n">
         <v>76.58186486338801</v>
@@ -36800,7 +36800,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K28" t="n">
-        <v>99.99837152068662</v>
+        <v>105.178570461152</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
         <v>649</v>
       </c>
       <c r="L29" t="n">
-        <v>448.3465428832665</v>
+        <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>174.322261376335</v>
       </c>
       <c r="O29" t="n">
         <v>164.7897032902292</v>
@@ -36897,7 +36897,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37064,10 +37064,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>113.6490400511193</v>
+        <v>108.4688411106541</v>
       </c>
       <c r="U31" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V31" t="n">
         <v>121.8296897837838</v>
@@ -37116,16 +37116,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>177.4460351758794</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>220.1374974874373</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
-        <v>649.0000000000022</v>
+        <v>174.3222613763352</v>
       </c>
       <c r="N32" t="n">
-        <v>481.0677468061043</v>
+        <v>649</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37134,7 +37134,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,13 +37353,13 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
       <c r="L35" t="n">
-        <v>562.0000000000001</v>
+        <v>561.0000000000246</v>
       </c>
       <c r="M35" t="n">
-        <v>90.83741289148684</v>
+        <v>561.0000000000047</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q35" t="n">
-        <v>562</v>
+        <v>89.87781693193469</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>195.7248986905059</v>
+        <v>193.5132771062241</v>
       </c>
       <c r="K36" t="n">
         <v>311.6274301124894</v>
@@ -37514,7 +37514,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L37" t="n">
-        <v>14.48250298976181</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>11.397136685873</v>
+        <v>25.87963967563485</v>
       </c>
       <c r="X37" t="n">
         <v>97.55635456989245</v>
@@ -37590,16 +37590,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K38" t="n">
-        <v>562</v>
+        <v>561.0000000000247</v>
       </c>
       <c r="L38" t="n">
-        <v>562.0000000000001</v>
+        <v>561.0000000000246</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>89.87781693193125</v>
       </c>
       <c r="N38" t="n">
-        <v>90.83741289148684</v>
+        <v>561.0000000000083</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37608,7 +37608,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q38" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37678,7 +37678,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451279</v>
       </c>
       <c r="O39" t="n">
         <v>419.0391822801049</v>
@@ -37721,25 +37721,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24.38809344142186</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>121.7922509475617</v>
+        <v>78.34042925558519</v>
       </c>
       <c r="I40" t="n">
         <v>187.184183724144</v>
@@ -37751,7 +37751,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L40" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37778,19 +37778,19 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U40" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37827,16 +37827,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
-        <v>562</v>
+        <v>430.7403194445352</v>
       </c>
       <c r="L41" t="n">
-        <v>562.0000000000001</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M41" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>90.83741289148706</v>
+        <v>561.0000000000083</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>561.0000000000083</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>195.7248986905059</v>
+        <v>193.5132771062241</v>
       </c>
       <c r="K42" t="n">
         <v>311.6274301124894</v>
@@ -37973,7 +37973,7 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>100.581864863388</v>
       </c>
       <c r="H43" t="n">
         <v>121.7922509475617</v>
@@ -37988,7 +37988,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38018,13 +38018,13 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>143.9034662083334</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>28.83909835518387</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -38064,10 +38064,10 @@
         <v>513.658479084785</v>
       </c>
       <c r="K44" t="n">
-        <v>222.5326763053304</v>
+        <v>561.0000000000246</v>
       </c>
       <c r="L44" t="n">
-        <v>562</v>
+        <v>220.5730803457936</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -38082,7 +38082,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>562</v>
+        <v>561.0000000000065</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38149,7 +38149,7 @@
         <v>436.150196103404</v>
       </c>
       <c r="M45" t="n">
-        <v>276.0650421645042</v>
+        <v>273.8534205802152</v>
       </c>
       <c r="N45" t="n">
         <v>328.7468614294096</v>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>72.27475335195533</v>
@@ -38204,7 +38204,7 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F46" t="n">
         <v>70.61714403225807</v>
@@ -38225,7 +38225,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38255,16 +38255,16 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>28.80619182792545</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>118.6271901612903</v>
+        <v>69.28333634879428</v>
       </c>
       <c r="X46" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
   </sheetData>
